--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/41.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/41.xlsx
@@ -426,13 +426,13 @@
         <v>-15.0315156463349</v>
       </c>
       <c r="E2">
-        <v>-15.48207581140323</v>
+        <v>-18.67015774059523</v>
       </c>
       <c r="F2">
-        <v>0.8706424738364645</v>
+        <v>0.1596321601292206</v>
       </c>
       <c r="G2">
-        <v>-12.47520604885135</v>
+        <v>-15.99897223939761</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.82852275340717</v>
       </c>
       <c r="E3">
-        <v>-15.35711257116157</v>
+        <v>-17.47937285790827</v>
       </c>
       <c r="F3">
-        <v>0.60612082589836</v>
+        <v>-0.1912909395845562</v>
       </c>
       <c r="G3">
-        <v>-12.13652399800175</v>
+        <v>-14.97315997750796</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.58540075420727</v>
       </c>
       <c r="E4">
-        <v>-14.65721879938009</v>
+        <v>-17.09971918252721</v>
       </c>
       <c r="F4">
-        <v>0.7678377880416283</v>
+        <v>0.2334003898174324</v>
       </c>
       <c r="G4">
-        <v>-13.08254549130389</v>
+        <v>-15.56873539638669</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.29757605302989</v>
       </c>
       <c r="E5">
-        <v>-15.5317078865273</v>
+        <v>-19.42788465392867</v>
       </c>
       <c r="F5">
-        <v>0.9823127453459309</v>
+        <v>-0.281154372491379</v>
       </c>
       <c r="G5">
-        <v>-12.1067952990591</v>
+        <v>-15.63468808462006</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.9742514974543</v>
       </c>
       <c r="E6">
-        <v>-15.5873220758155</v>
+        <v>-18.96815397266997</v>
       </c>
       <c r="F6">
-        <v>1.030452654057544</v>
+        <v>-0.6270476222177201</v>
       </c>
       <c r="G6">
-        <v>-12.27375273169562</v>
+        <v>-15.98008723236884</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.61421165557118</v>
       </c>
       <c r="E7">
-        <v>-16.58299765588198</v>
+        <v>-19.65479290103101</v>
       </c>
       <c r="F7">
-        <v>1.150001862496321</v>
+        <v>0.3076017630735168</v>
       </c>
       <c r="G7">
-        <v>-12.11186043373418</v>
+        <v>-15.46047062561591</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.20598239427351</v>
       </c>
       <c r="E8">
-        <v>-18.11663783416367</v>
+        <v>-20.60727589601233</v>
       </c>
       <c r="F8">
-        <v>1.545546668230562</v>
+        <v>-0.4899066084702412</v>
       </c>
       <c r="G8">
-        <v>-12.17635648193026</v>
+        <v>-14.94093678250146</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.73294106472742</v>
       </c>
       <c r="E9">
-        <v>-18.5458647145067</v>
+        <v>-22.00404294741218</v>
       </c>
       <c r="F9">
-        <v>1.252035283510339</v>
+        <v>1.134856882826974</v>
       </c>
       <c r="G9">
-        <v>-12.6539424025166</v>
+        <v>-16.14442767875657</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.19968580193317</v>
       </c>
       <c r="E10">
-        <v>-19.40476226564551</v>
+        <v>-21.48086381683202</v>
       </c>
       <c r="F10">
-        <v>1.256067398771048</v>
+        <v>0.1360436523717078</v>
       </c>
       <c r="G10">
-        <v>-12.38635762766839</v>
+        <v>-15.6151426237562</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.60154988751838</v>
       </c>
       <c r="E11">
-        <v>-18.78073854738853</v>
+        <v>-22.75016791033798</v>
       </c>
       <c r="F11">
-        <v>1.565507697588761</v>
+        <v>0.1849500747463933</v>
       </c>
       <c r="G11">
-        <v>-11.23002710789298</v>
+        <v>-14.65808873744444</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.93501324187301</v>
       </c>
       <c r="E12">
-        <v>-20.32812717275751</v>
+        <v>-24.48052047103886</v>
       </c>
       <c r="F12">
-        <v>1.419553360421862</v>
+        <v>0.7913859112982974</v>
       </c>
       <c r="G12">
-        <v>-10.77384386421802</v>
+        <v>-15.56417511990635</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.19930368170749</v>
       </c>
       <c r="E13">
-        <v>-19.69560350878814</v>
+        <v>-22.68332763398476</v>
       </c>
       <c r="F13">
-        <v>1.772992176982314</v>
+        <v>0.6492815632118313</v>
       </c>
       <c r="G13">
-        <v>-10.66983976555628</v>
+        <v>-15.22103376421535</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.420532906235019</v>
       </c>
       <c r="E14">
-        <v>-21.10286303446376</v>
+        <v>-22.93146989570906</v>
       </c>
       <c r="F14">
-        <v>1.704767709851098</v>
+        <v>0.418246585002736</v>
       </c>
       <c r="G14">
-        <v>-9.99902061238822</v>
+        <v>-12.45011542420922</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.615599428426792</v>
       </c>
       <c r="E15">
-        <v>-21.75728639873423</v>
+        <v>-25.17828586003673</v>
       </c>
       <c r="F15">
-        <v>2.212809481582665</v>
+        <v>1.302553918506941</v>
       </c>
       <c r="G15">
-        <v>-10.01091540251082</v>
+        <v>-11.94360195670072</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.79996874714416</v>
       </c>
       <c r="E16">
-        <v>-24.40434700975583</v>
+        <v>-25.12133577091628</v>
       </c>
       <c r="F16">
-        <v>2.165280883354411</v>
+        <v>1.315126959769615</v>
       </c>
       <c r="G16">
-        <v>-8.478847895664746</v>
+        <v>-12.72077238531787</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.987086727562938</v>
       </c>
       <c r="E17">
-        <v>-23.32342290649496</v>
+        <v>-25.71844223967166</v>
       </c>
       <c r="F17">
-        <v>2.707609888155242</v>
+        <v>0.9652752371076333</v>
       </c>
       <c r="G17">
-        <v>-8.855326444936203</v>
+        <v>-12.78508966405483</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.200494324338832</v>
       </c>
       <c r="E18">
-        <v>-23.36277081714761</v>
+        <v>-28.51050458841887</v>
       </c>
       <c r="F18">
-        <v>2.438995944131642</v>
+        <v>0.77586242591516</v>
       </c>
       <c r="G18">
-        <v>-7.221065707838364</v>
+        <v>-11.64263695118004</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.4485618752887</v>
       </c>
       <c r="E19">
-        <v>-26.00506747351314</v>
+        <v>-28.39666328034004</v>
       </c>
       <c r="F19">
-        <v>2.862664199512257</v>
+        <v>1.315782614018607</v>
       </c>
       <c r="G19">
-        <v>-6.727569305390287</v>
+        <v>-10.84425254674724</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.733872457009451</v>
       </c>
       <c r="E20">
-        <v>-26.65261208576596</v>
+        <v>-30.61794997244947</v>
       </c>
       <c r="F20">
-        <v>3.085211305867554</v>
+        <v>1.486491858349741</v>
       </c>
       <c r="G20">
-        <v>-6.664619281961046</v>
+        <v>-11.50130645156301</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.058750936462338</v>
       </c>
       <c r="E21">
-        <v>-27.42382932316825</v>
+        <v>-29.73292312628641</v>
       </c>
       <c r="F21">
-        <v>2.868148573097423</v>
+        <v>1.870401176723248</v>
       </c>
       <c r="G21">
-        <v>-6.453793810383639</v>
+        <v>-10.2386743145216</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.432421066148447</v>
       </c>
       <c r="E22">
-        <v>-28.65000423022515</v>
+        <v>-31.38423117318341</v>
       </c>
       <c r="F22">
-        <v>2.912053652191151</v>
+        <v>2.015110721040612</v>
       </c>
       <c r="G22">
-        <v>-5.731793623178446</v>
+        <v>-9.977511998019576</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.855761921396041</v>
       </c>
       <c r="E23">
-        <v>-28.88123717000482</v>
+        <v>-31.96087573213513</v>
       </c>
       <c r="F23">
-        <v>2.783569174977464</v>
+        <v>2.468229571624739</v>
       </c>
       <c r="G23">
-        <v>-5.280417291626516</v>
+        <v>-8.933998249131445</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.327835208788581</v>
       </c>
       <c r="E24">
-        <v>-28.26240308296063</v>
+        <v>-33.24277577609342</v>
       </c>
       <c r="F24">
-        <v>3.29113900234623</v>
+        <v>1.925088125689288</v>
       </c>
       <c r="G24">
-        <v>-4.660342180484405</v>
+        <v>-9.6089224787682</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.849916130688358</v>
       </c>
       <c r="E25">
-        <v>-29.65143550075538</v>
+        <v>-33.63646092818725</v>
       </c>
       <c r="F25">
-        <v>2.936661274705249</v>
+        <v>2.326405539485305</v>
       </c>
       <c r="G25">
-        <v>-4.91932284747605</v>
+        <v>-11.04370629439726</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.425065447338547</v>
       </c>
       <c r="E26">
-        <v>-29.41764397316139</v>
+        <v>-33.47991384597908</v>
       </c>
       <c r="F26">
-        <v>2.971734025908571</v>
+        <v>2.027916567072856</v>
       </c>
       <c r="G26">
-        <v>-4.624277097379585</v>
+        <v>-9.488938376788395</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.049564532447321</v>
       </c>
       <c r="E27">
-        <v>-30.19621092387813</v>
+        <v>-31.61072280067704</v>
       </c>
       <c r="F27">
-        <v>3.277218227349517</v>
+        <v>2.009859152225015</v>
       </c>
       <c r="G27">
-        <v>-3.966359140178064</v>
+        <v>-8.397461444127302</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.7178818693336513</v>
       </c>
       <c r="E28">
-        <v>-30.84418347692467</v>
+        <v>-33.00857442160173</v>
       </c>
       <c r="F28">
-        <v>3.191536569912413</v>
+        <v>2.057126438977221</v>
       </c>
       <c r="G28">
-        <v>-4.702131196826625</v>
+        <v>-10.35726136628383</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.4271115582440647</v>
       </c>
       <c r="E29">
-        <v>-29.23830734550963</v>
+        <v>-35.03787872239297</v>
       </c>
       <c r="F29">
-        <v>3.090969660576092</v>
+        <v>1.966614478498025</v>
       </c>
       <c r="G29">
-        <v>-3.763627952444176</v>
+        <v>-8.248423994494853</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.1750432453608994</v>
       </c>
       <c r="E30">
-        <v>-30.16916914134132</v>
+        <v>-33.33543741123837</v>
       </c>
       <c r="F30">
-        <v>3.06771769032561</v>
+        <v>2.510055244851495</v>
       </c>
       <c r="G30">
-        <v>-4.416060335687123</v>
+        <v>-7.227468302911315</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.04284295719729524</v>
       </c>
       <c r="E31">
-        <v>-29.67451034006147</v>
+        <v>-32.29970295010003</v>
       </c>
       <c r="F31">
-        <v>3.277289494115712</v>
+        <v>2.927195464448668</v>
       </c>
       <c r="G31">
-        <v>-3.846663055660176</v>
+        <v>-8.954328309288108</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.2308161868402765</v>
       </c>
       <c r="E32">
-        <v>-28.37297483280592</v>
+        <v>-33.04811705663671</v>
       </c>
       <c r="F32">
-        <v>2.921555887683788</v>
+        <v>2.352115421316549</v>
       </c>
       <c r="G32">
-        <v>-4.674342477569983</v>
+        <v>-9.166891817273633</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.389815540509062</v>
       </c>
       <c r="E33">
-        <v>-29.57408463623037</v>
+        <v>-32.23400611343376</v>
       </c>
       <c r="F33">
-        <v>3.061327436956812</v>
+        <v>2.357268800365389</v>
       </c>
       <c r="G33">
-        <v>-4.039628134053214</v>
+        <v>-9.185205755196881</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.5202623199313535</v>
       </c>
       <c r="E34">
-        <v>-28.40693385938944</v>
+        <v>-32.53193441839839</v>
       </c>
       <c r="F34">
-        <v>3.279313470275643</v>
+        <v>1.960705671727521</v>
       </c>
       <c r="G34">
-        <v>-4.516972384815188</v>
+        <v>-8.515157959139472</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.6226354608540079</v>
       </c>
       <c r="E35">
-        <v>-28.90646982717556</v>
+        <v>-32.80168202961329</v>
       </c>
       <c r="F35">
-        <v>3.48398053684563</v>
+        <v>2.240242435449907</v>
       </c>
       <c r="G35">
-        <v>-5.139546957839449</v>
+        <v>-9.591886411423111</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.6965811324428258</v>
       </c>
       <c r="E36">
-        <v>-27.60216062959031</v>
+        <v>-33.29356487632644</v>
       </c>
       <c r="F36">
-        <v>3.361788123233984</v>
+        <v>1.696025653197872</v>
       </c>
       <c r="G36">
-        <v>-5.048867804973272</v>
+        <v>-10.39131694824632</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.7390767734610918</v>
       </c>
       <c r="E37">
-        <v>-27.83838394772643</v>
+        <v>-31.97840092654481</v>
       </c>
       <c r="F37">
-        <v>3.270371866677073</v>
+        <v>1.714553428702598</v>
       </c>
       <c r="G37">
-        <v>-5.064222115184411</v>
+        <v>-10.39841475788251</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.7474162438850054</v>
       </c>
       <c r="E38">
-        <v>-27.83548572436152</v>
+        <v>-30.99320876380609</v>
       </c>
       <c r="F38">
-        <v>3.030278882484621</v>
+        <v>2.106165892648803</v>
       </c>
       <c r="G38">
-        <v>-5.609270332770019</v>
+        <v>-10.3112811992889</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.7198347286000005</v>
       </c>
       <c r="E39">
-        <v>-26.75434878282228</v>
+        <v>-30.62252146696022</v>
       </c>
       <c r="F39">
-        <v>3.510588379930928</v>
+        <v>1.544959113335934</v>
       </c>
       <c r="G39">
-        <v>-6.058349145717695</v>
+        <v>-9.891586788547793</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.6560901202464999</v>
       </c>
       <c r="E40">
-        <v>-25.84003629525161</v>
+        <v>-29.83126346783698</v>
       </c>
       <c r="F40">
-        <v>3.41176037968976</v>
+        <v>2.126495925485299</v>
       </c>
       <c r="G40">
-        <v>-6.075633503978231</v>
+        <v>-9.20655546337964</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.555951531105752</v>
       </c>
       <c r="E41">
-        <v>-26.19068962308755</v>
+        <v>-28.60678447429595</v>
       </c>
       <c r="F41">
-        <v>3.42459156501665</v>
+        <v>2.025933767266725</v>
       </c>
       <c r="G41">
-        <v>-6.581279608555433</v>
+        <v>-11.107162831294</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.4213372433022746</v>
       </c>
       <c r="E42">
-        <v>-25.53786481014179</v>
+        <v>-27.72286257579076</v>
       </c>
       <c r="F42">
-        <v>3.653267613264699</v>
+        <v>2.248529968505401</v>
       </c>
       <c r="G42">
-        <v>-7.441041527286317</v>
+        <v>-11.01876464430438</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.2561231250592254</v>
       </c>
       <c r="E43">
-        <v>-24.27804786968191</v>
+        <v>-28.17269854134269</v>
       </c>
       <c r="F43">
-        <v>4.134414891140272</v>
+        <v>2.821628795537305</v>
       </c>
       <c r="G43">
-        <v>-7.318991644890006</v>
+        <v>-11.25720668677039</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.06447537683525237</v>
       </c>
       <c r="E44">
-        <v>-24.03865461974042</v>
+        <v>-27.00000944079038</v>
       </c>
       <c r="F44">
-        <v>3.955894809234192</v>
+        <v>3.102381845402749</v>
       </c>
       <c r="G44">
-        <v>-7.553381579615945</v>
+        <v>-11.48529334278956</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.1504852664537278</v>
       </c>
       <c r="E45">
-        <v>-23.22664036000303</v>
+        <v>-25.74085365753562</v>
       </c>
       <c r="F45">
-        <v>4.381924370134727</v>
+        <v>3.169692514220756</v>
       </c>
       <c r="G45">
-        <v>-7.585987142632227</v>
+        <v>-11.12607266741432</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.3857591441142222</v>
       </c>
       <c r="E46">
-        <v>-22.12742122175116</v>
+        <v>-25.47658097139599</v>
       </c>
       <c r="F46">
-        <v>4.391852622518616</v>
+        <v>3.376519755659401</v>
       </c>
       <c r="G46">
-        <v>-8.503832582849626</v>
+        <v>-11.20218210936217</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.6370869443692726</v>
       </c>
       <c r="E47">
-        <v>-23.07130464459192</v>
+        <v>-27.15420398075156</v>
       </c>
       <c r="F47">
-        <v>4.085405527881083</v>
+        <v>3.339299499234744</v>
       </c>
       <c r="G47">
-        <v>-8.047950598818746</v>
+        <v>-13.26365219557526</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.9017369959841921</v>
       </c>
       <c r="E48">
-        <v>-20.43812380640382</v>
+        <v>-24.47258205610341</v>
       </c>
       <c r="F48">
-        <v>4.364617631890805</v>
+        <v>2.445169229790025</v>
       </c>
       <c r="G48">
-        <v>-8.210524869161276</v>
+        <v>-13.82200549568319</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.177751333211716</v>
       </c>
       <c r="E49">
-        <v>-20.53919934625502</v>
+        <v>-25.55208421852588</v>
       </c>
       <c r="F49">
-        <v>4.030370163613648</v>
+        <v>2.300985475836587</v>
       </c>
       <c r="G49">
-        <v>-7.508017174091313</v>
+        <v>-11.59909003515647</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.463089046500578</v>
       </c>
       <c r="E50">
-        <v>-21.14579749653048</v>
+        <v>-23.14381457040274</v>
       </c>
       <c r="F50">
-        <v>4.12887350414215</v>
+        <v>3.523034724720366</v>
       </c>
       <c r="G50">
-        <v>-7.205102257247999</v>
+        <v>-13.30131958272108</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.753081079656603</v>
       </c>
       <c r="E51">
-        <v>-18.46249550802549</v>
+        <v>-24.13900107527639</v>
       </c>
       <c r="F51">
-        <v>4.184135338355494</v>
+        <v>2.554945389024626</v>
       </c>
       <c r="G51">
-        <v>-8.023975628023345</v>
+        <v>-13.16124377986344</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.044944571249598</v>
       </c>
       <c r="E52">
-        <v>-18.72963018973796</v>
+        <v>-23.34400934933383</v>
       </c>
       <c r="F52">
-        <v>4.462275273460462</v>
+        <v>3.457108214872453</v>
       </c>
       <c r="G52">
-        <v>-8.731780195956143</v>
+        <v>-14.08696004210046</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.335984630231247</v>
       </c>
       <c r="E53">
-        <v>-17.75999333521559</v>
+        <v>-22.46409062185142</v>
       </c>
       <c r="F53">
-        <v>4.620468489941878</v>
+        <v>3.572866031349669</v>
       </c>
       <c r="G53">
-        <v>-9.234456741184619</v>
+        <v>-13.46845909536227</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.62306723394711</v>
       </c>
       <c r="E54">
-        <v>-18.42032635806606</v>
+        <v>-21.56770636287711</v>
       </c>
       <c r="F54">
-        <v>4.781738847016992</v>
+        <v>3.14965071586087</v>
       </c>
       <c r="G54">
-        <v>-9.16826900421797</v>
+        <v>-13.40330093805833</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.89962044767924</v>
       </c>
       <c r="E55">
-        <v>-18.2203851736794</v>
+        <v>-21.57294580730399</v>
       </c>
       <c r="F55">
-        <v>4.377496328395158</v>
+        <v>2.862037051969743</v>
       </c>
       <c r="G55">
-        <v>-8.937659712497878</v>
+        <v>-13.04396439358922</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.162593235213223</v>
       </c>
       <c r="E56">
-        <v>-16.7875759976525</v>
+        <v>-20.02856861715011</v>
       </c>
       <c r="F56">
-        <v>4.499055259640628</v>
+        <v>3.196900581848006</v>
       </c>
       <c r="G56">
-        <v>-9.0367642037615</v>
+        <v>-13.80280764210096</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.409066342905712</v>
       </c>
       <c r="E57">
-        <v>-15.62373100683717</v>
+        <v>-21.15381742399807</v>
       </c>
       <c r="F57">
-        <v>4.309072314318596</v>
+        <v>3.32946626920578</v>
       </c>
       <c r="G57">
-        <v>-9.545230893138163</v>
+        <v>-14.75425677481473</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.635777085051093</v>
       </c>
       <c r="E58">
-        <v>-15.41387699284772</v>
+        <v>-17.26822370035262</v>
       </c>
       <c r="F58">
-        <v>4.106386463848826</v>
+        <v>2.881361431549935</v>
       </c>
       <c r="G58">
-        <v>-9.504077501539482</v>
+        <v>-14.3117444289442</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.835932418752793</v>
       </c>
       <c r="E59">
-        <v>-16.02867168107706</v>
+        <v>-18.84242994879502</v>
       </c>
       <c r="F59">
-        <v>4.398117763120095</v>
+        <v>2.880229081820396</v>
       </c>
       <c r="G59">
-        <v>-9.867522433022829</v>
+        <v>-12.62064824602815</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.008773712051572</v>
       </c>
       <c r="E60">
-        <v>-16.04878716261913</v>
+        <v>-17.64380627760079</v>
       </c>
       <c r="F60">
-        <v>4.400366625520019</v>
+        <v>3.058003238240305</v>
       </c>
       <c r="G60">
-        <v>-8.407273901105702</v>
+        <v>-14.93290208847765</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.153550978512238</v>
       </c>
       <c r="E61">
-        <v>-13.89845486549889</v>
+        <v>-16.85192108482749</v>
       </c>
       <c r="F61">
-        <v>3.846975434899844</v>
+        <v>3.065294620274988</v>
       </c>
       <c r="G61">
-        <v>-9.282105423131348</v>
+        <v>-13.05656432991169</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.269556107440622</v>
       </c>
       <c r="E62">
-        <v>-14.71277864698019</v>
+        <v>-17.39284730504371</v>
       </c>
       <c r="F62">
-        <v>4.028672430872296</v>
+        <v>3.033349688254658</v>
       </c>
       <c r="G62">
-        <v>-9.723626260612869</v>
+        <v>-13.21807922568165</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.353659963661027</v>
       </c>
       <c r="E63">
-        <v>-13.72876388748346</v>
+        <v>-17.91613964747407</v>
       </c>
       <c r="F63">
-        <v>3.700191235833254</v>
+        <v>2.142030496809845</v>
       </c>
       <c r="G63">
-        <v>-9.699167950168732</v>
+        <v>-13.48567724271202</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.409966160541901</v>
       </c>
       <c r="E64">
-        <v>-13.97065232660318</v>
+        <v>-16.17432099058576</v>
       </c>
       <c r="F64">
-        <v>3.241676699195225</v>
+        <v>2.502817708817936</v>
       </c>
       <c r="G64">
-        <v>-9.425485150437185</v>
+        <v>-14.87692572922689</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.442303606941993</v>
       </c>
       <c r="E65">
-        <v>-12.42878391104955</v>
+        <v>-18.27744394617605</v>
       </c>
       <c r="F65">
-        <v>3.807983011555809</v>
+        <v>1.866231279047896</v>
       </c>
       <c r="G65">
-        <v>-9.587427106581712</v>
+        <v>-13.71139354812507</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.453242110670058</v>
       </c>
       <c r="E66">
-        <v>-13.21859506272734</v>
+        <v>-17.52796338401057</v>
       </c>
       <c r="F66">
-        <v>3.023689082170478</v>
+        <v>1.728166964751716</v>
       </c>
       <c r="G66">
-        <v>-9.323904371110187</v>
+        <v>-14.13556050588973</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.442282432589309</v>
       </c>
       <c r="E67">
-        <v>-13.50355834660801</v>
+        <v>-16.54254026909745</v>
       </c>
       <c r="F67">
-        <v>3.328297494240186</v>
+        <v>2.301420994963333</v>
       </c>
       <c r="G67">
-        <v>-8.616632801009212</v>
+        <v>-13.71488451839623</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.41536425986199</v>
       </c>
       <c r="E68">
-        <v>-12.44294897774554</v>
+        <v>-15.2869302809907</v>
       </c>
       <c r="F68">
-        <v>2.828369047913415</v>
+        <v>0.8157686475724032</v>
       </c>
       <c r="G68">
-        <v>-9.934143851455124</v>
+        <v>-14.26418016590872</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.376506028098686</v>
       </c>
       <c r="E69">
-        <v>-12.51916772376864</v>
+        <v>-15.29459698748568</v>
       </c>
       <c r="F69">
-        <v>2.622355831315306</v>
+        <v>1.351968710480483</v>
       </c>
       <c r="G69">
-        <v>-8.657054562043713</v>
+        <v>-13.91464449150862</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.327464831514217</v>
       </c>
       <c r="E70">
-        <v>-12.52689330042573</v>
+        <v>-17.40091251725137</v>
       </c>
       <c r="F70">
-        <v>2.606791169578367</v>
+        <v>2.027455708651463</v>
       </c>
       <c r="G70">
-        <v>-9.341930291571519</v>
+        <v>-12.58438121964544</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.267139402499461</v>
       </c>
       <c r="E71">
-        <v>-12.26568186271529</v>
+        <v>-15.94809201458458</v>
       </c>
       <c r="F71">
-        <v>2.144399720859342</v>
+        <v>1.604694916760395</v>
       </c>
       <c r="G71">
-        <v>-9.141311231891684</v>
+        <v>-11.81217991988274</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.200973381180293</v>
       </c>
       <c r="E72">
-        <v>-12.92904443467689</v>
+        <v>-17.69915781539654</v>
       </c>
       <c r="F72">
-        <v>2.465597452393278</v>
+        <v>1.566380319548168</v>
       </c>
       <c r="G72">
-        <v>-8.298443027047702</v>
+        <v>-13.83627891277576</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.131441563478871</v>
       </c>
       <c r="E73">
-        <v>-12.05683316995554</v>
+        <v>-14.72259185015482</v>
       </c>
       <c r="F73">
-        <v>2.047921940196686</v>
+        <v>1.669286362521593</v>
       </c>
       <c r="G73">
-        <v>-8.34891560433943</v>
+        <v>-13.29551950693628</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.058617750967525</v>
       </c>
       <c r="E74">
-        <v>-13.16286313311494</v>
+        <v>-16.97318456180489</v>
       </c>
       <c r="F74">
-        <v>2.562593104890283</v>
+        <v>0.7056424893304903</v>
       </c>
       <c r="G74">
-        <v>-8.726178752903696</v>
+        <v>-12.80063598590725</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.980622426800319</v>
       </c>
       <c r="E75">
-        <v>-12.71957534097809</v>
+        <v>-17.69980538717964</v>
       </c>
       <c r="F75">
-        <v>2.159467098938833</v>
+        <v>0.6212547196262993</v>
       </c>
       <c r="G75">
-        <v>-7.796147194556241</v>
+        <v>-11.7312834290851</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.902786640639476</v>
       </c>
       <c r="E76">
-        <v>-12.96591979852135</v>
+        <v>-17.6493627152082</v>
       </c>
       <c r="F76">
-        <v>2.422175403603759</v>
+        <v>1.263249505097565</v>
       </c>
       <c r="G76">
-        <v>-7.831904396925909</v>
+        <v>-11.39412753972911</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.826627690221459</v>
       </c>
       <c r="E77">
-        <v>-14.22036596880814</v>
+        <v>-17.2921204576911</v>
       </c>
       <c r="F77">
-        <v>2.05730381403975</v>
+        <v>0.5221844123800693</v>
       </c>
       <c r="G77">
-        <v>-7.621052440984188</v>
+        <v>-10.58087547527945</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.751115559211771</v>
       </c>
       <c r="E78">
-        <v>-13.55472104594667</v>
+        <v>-17.98267198759476</v>
       </c>
       <c r="F78">
-        <v>1.72506448486337</v>
+        <v>0.2860491092703014</v>
       </c>
       <c r="G78">
-        <v>-7.217397623380852</v>
+        <v>-12.91291975896271</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.673595129693017</v>
       </c>
       <c r="E79">
-        <v>-13.13261745521771</v>
+        <v>-17.51092726479371</v>
       </c>
       <c r="F79">
-        <v>1.908872560821103</v>
+        <v>0.4820881460129733</v>
       </c>
       <c r="G79">
-        <v>-6.778442458692267</v>
+        <v>-9.736517524942791</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.598063333290271</v>
       </c>
       <c r="E80">
-        <v>-14.52735122178812</v>
+        <v>-18.59225893071528</v>
       </c>
       <c r="F80">
-        <v>2.039048435952479</v>
+        <v>0.6321490326186073</v>
       </c>
       <c r="G80">
-        <v>-6.747015449887966</v>
+        <v>-10.28482662988458</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.524436021566968</v>
       </c>
       <c r="E81">
-        <v>-15.44713863443406</v>
+        <v>-18.76106685629921</v>
       </c>
       <c r="F81">
-        <v>1.94003355841329</v>
+        <v>0.618921920812857</v>
       </c>
       <c r="G81">
-        <v>-6.803013327684738</v>
+        <v>-9.249413785931045</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.450670707378479</v>
       </c>
       <c r="E82">
-        <v>-16.23340851943785</v>
+        <v>-17.11724437693689</v>
       </c>
       <c r="F82">
-        <v>1.873641439026237</v>
+        <v>0.3795669435770007</v>
       </c>
       <c r="G82">
-        <v>-6.16357814622897</v>
+        <v>-10.35380515674083</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.375149356235685</v>
       </c>
       <c r="E83">
-        <v>-17.48544101307855</v>
+        <v>-20.26676182147957</v>
       </c>
       <c r="F83">
-        <v>1.830312828885729</v>
+        <v>0.1899918025281948</v>
       </c>
       <c r="G83">
-        <v>-6.090137003985777</v>
+        <v>-8.61260386708792</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.301135992163278</v>
       </c>
       <c r="E84">
-        <v>-17.36600703960025</v>
+        <v>-20.57059072807619</v>
       </c>
       <c r="F84">
-        <v>2.131300889232743</v>
+        <v>0.7606271750086325</v>
       </c>
       <c r="G84">
-        <v>-5.290007942053784</v>
+        <v>-8.474279342820552</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.227633395033835</v>
       </c>
       <c r="E85">
-        <v>-17.79529731857938</v>
+        <v>-23.77751110914009</v>
       </c>
       <c r="F85">
-        <v>1.26751917624559</v>
+        <v>0.03860456221838032</v>
       </c>
       <c r="G85">
-        <v>-4.962922732228252</v>
+        <v>-8.407254037832466</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.151223473576805</v>
       </c>
       <c r="E86">
-        <v>-19.20892387870979</v>
+        <v>-26.5161419930708</v>
       </c>
       <c r="F86">
-        <v>1.420285032554795</v>
+        <v>0.5070053830335399</v>
       </c>
       <c r="G86">
-        <v>-5.417218964945819</v>
+        <v>-8.286352914738282</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.070674962048879</v>
       </c>
       <c r="E87">
-        <v>-21.18125544801054</v>
+        <v>-23.98214832107271</v>
       </c>
       <c r="F87">
-        <v>1.667230712243352</v>
+        <v>0.4666533481611005</v>
       </c>
       <c r="G87">
-        <v>-5.136603882855036</v>
+        <v>-7.774489605638329</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.988809155394974</v>
       </c>
       <c r="E88">
-        <v>-22.42870965442949</v>
+        <v>-26.5915908985126</v>
       </c>
       <c r="F88">
-        <v>1.775342396560826</v>
+        <v>0.5889439515395037</v>
       </c>
       <c r="G88">
-        <v>-5.23365914642985</v>
+        <v>-8.337755755326546</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.906269807637371</v>
       </c>
       <c r="E89">
-        <v>-24.24542474293065</v>
+        <v>-27.01772030263438</v>
       </c>
       <c r="F89">
-        <v>0.9880916882313694</v>
+        <v>-0.1825575933138654</v>
       </c>
       <c r="G89">
-        <v>-4.655422709813048</v>
+        <v>-8.599364995476373</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.822005597948632</v>
       </c>
       <c r="E90">
-        <v>-24.76805139968188</v>
+        <v>-27.2176931863391</v>
       </c>
       <c r="F90">
-        <v>1.221276547220674</v>
+        <v>0.359761117398515</v>
       </c>
       <c r="G90">
-        <v>-3.472041722436248</v>
+        <v>-8.585387872209571</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.738067071184309</v>
       </c>
       <c r="E91">
-        <v>-24.07593754624557</v>
+        <v>-29.94511156862681</v>
       </c>
       <c r="F91">
-        <v>1.417268072785882</v>
+        <v>-0.01622729583892195</v>
       </c>
       <c r="G91">
-        <v>-4.846864937258022</v>
+        <v>-8.02399880184212</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.657481953725236</v>
       </c>
       <c r="E92">
-        <v>-27.77228181263646</v>
+        <v>-33.11968279561692</v>
       </c>
       <c r="F92">
-        <v>1.350586135216305</v>
+        <v>-0.6903491395107926</v>
       </c>
       <c r="G92">
-        <v>-5.289945041688538</v>
+        <v>-7.506060641677603</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.580193181878986</v>
       </c>
       <c r="E93">
-        <v>-29.0866215801487</v>
+        <v>-31.36646596965131</v>
       </c>
       <c r="F93">
-        <v>1.142457087515168</v>
+        <v>0.07917118924236176</v>
       </c>
       <c r="G93">
-        <v>-4.683883469814162</v>
+        <v>-8.20373825080577</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.503151687868734</v>
       </c>
       <c r="E94">
-        <v>-30.40747102904696</v>
+        <v>-34.92041689934502</v>
       </c>
       <c r="F94">
-        <v>1.094532562808055</v>
+        <v>-0.2566473153029113</v>
       </c>
       <c r="G94">
-        <v>-4.856299992044945</v>
+        <v>-7.386622779711777</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.425947712190284</v>
       </c>
       <c r="E95">
-        <v>-32.17029501261985</v>
+        <v>-35.81503052498232</v>
       </c>
       <c r="F95">
-        <v>0.8365199461824062</v>
+        <v>-0.08505990604166665</v>
       </c>
       <c r="G95">
-        <v>-4.671141180033508</v>
+        <v>-8.512592286346536</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.346803582654362</v>
       </c>
       <c r="E96">
-        <v>-34.89615333561192</v>
+        <v>-37.45097345957129</v>
       </c>
       <c r="F96">
-        <v>1.019841824424099</v>
+        <v>0.2260401165754275</v>
       </c>
       <c r="G96">
-        <v>-3.808657992869342</v>
+        <v>-6.137997560847021</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.261797718037359</v>
       </c>
       <c r="E97">
-        <v>-36.6299316868996</v>
+        <v>-37.73328758615747</v>
       </c>
       <c r="F97">
-        <v>0.7916709783630765</v>
+        <v>-0.02609457554506743</v>
       </c>
       <c r="G97">
-        <v>-5.565653895290121</v>
+        <v>-8.093010434153767</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.164553671944507</v>
       </c>
       <c r="E98">
-        <v>-39.6587290713458</v>
+        <v>-40.73371634518262</v>
       </c>
       <c r="F98">
-        <v>1.18257552576508</v>
+        <v>-0.9819379052496727</v>
       </c>
       <c r="G98">
-        <v>-3.799702967185614</v>
+        <v>-8.636661601521803</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.054133733711715</v>
       </c>
       <c r="E99">
-        <v>-41.07333604609887</v>
+        <v>-43.53261668968142</v>
       </c>
       <c r="F99">
-        <v>0.6946879955133957</v>
+        <v>-0.2245368860144188</v>
       </c>
       <c r="G99">
-        <v>-4.788433808489886</v>
+        <v>-9.94647232304337</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.928100788110269</v>
       </c>
       <c r="E100">
-        <v>-42.28074948534199</v>
+        <v>-45.26339719117603</v>
       </c>
       <c r="F100">
-        <v>0.3752663901636249</v>
+        <v>-0.8287753306086506</v>
       </c>
       <c r="G100">
-        <v>-4.412908696333737</v>
+        <v>-9.395518092215701</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.788188017400389</v>
       </c>
       <c r="E101">
-        <v>-45.23142842891887</v>
+        <v>-47.92876189413663</v>
       </c>
       <c r="F101">
-        <v>0.5489545853216999</v>
+        <v>-1.194649406017134</v>
       </c>
       <c r="G101">
-        <v>-4.715095293158411</v>
+        <v>-8.049970031597702</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.631236278299275</v>
       </c>
       <c r="E102">
-        <v>-47.4726675775061</v>
+        <v>-48.02561010350168</v>
       </c>
       <c r="F102">
-        <v>0.5640702664316117</v>
+        <v>-0.6095025362335242</v>
       </c>
       <c r="G102">
-        <v>-6.034437075287539</v>
+        <v>-8.879314657913763</v>
       </c>
     </row>
   </sheetData>
